--- a/experiment/SRForm2_bestx4/Test/results-Set5/Set5.xlsx
+++ b/experiment/SRForm2_bestx4/Test/results-Set5/Set5.xlsx
@@ -455,7 +455,7 @@
         <v>33.63</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8925</v>
+        <v>0.8923</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34.18</v>
+        <v>34.47</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.9376</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27.89</v>
+        <v>28.04</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9086</v>
+        <v>0.9116</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32.84</v>
+        <v>32.88</v>
       </c>
       <c r="C5" t="n">
-        <v>0.794</v>
+        <v>0.795</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.43</v>
+        <v>30.45</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9092</v>
+        <v>0.9106</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8877</v>
+        <v>0.8894</v>
       </c>
     </row>
   </sheetData>
